--- a/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
+++ b/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27720"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\bldgs\BPSfDSPC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Richa.richa\Downloads\BPSfDSPC\BPSfDSPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B358AC65-4386-4D6B-A447-C59C227A0A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{C4CD6C72-4998-4F43-948F-FC077E0F061A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E19FBF4E-07E7-4597-84B9-E1CCC548F6AD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="7" r:id="rId1"/>
     <sheet name="BPSfDSPV" sheetId="8" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -25,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,24 +37,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>BPSfDSPC BAU Percent Subsidy for Distributed Solar PV Capacity</t>
+  </si>
+  <si>
+    <t>MNRE (Annual Report 2023)</t>
+  </si>
   <si>
     <t>Sources:</t>
   </si>
   <si>
-    <t>urban residential</t>
-  </si>
-  <si>
-    <t>rural residential</t>
-  </si>
-  <si>
-    <t>commercial</t>
-  </si>
-  <si>
-    <t>Percent Subsidy (Dmnl)</t>
-  </si>
-  <si>
-    <t>None needed</t>
+    <t>https://cdnbbsr.s3waas.gov.in/s3716e1b8c6cd17b771da77391355749f3/uploads/2023/08/2023080211.pdf</t>
   </si>
   <si>
     <r>
@@ -63,18 +62,27 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">We include the 30% 25D credit included in the Inflation Reduction Act, which is phased out through 2035. </t>
+      <t xml:space="preserve">We are calculating percentage of subsidy (CFA) per KW to Total Cost of Solar Rooftop per KW </t>
     </r>
   </si>
   <si>
-    <t>BPSfDSPC BAU Percent Subsidy for Distributed Solar PV Capacity</t>
+    <t>Percent Subsidy (Dmnl)</t>
+  </si>
+  <si>
+    <t>urban residential</t>
+  </si>
+  <si>
+    <t>rural residential</t>
+  </si>
+  <si>
+    <t>commercial</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -121,7 +129,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -141,9 +148,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -181,9 +188,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -216,26 +223,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -268,26 +258,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -462,31 +435,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="61.5703125" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -500,16 +478,16 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AZ7"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52">
       <c r="A1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -601,303 +579,717 @@
       <c r="AE1">
         <v>2050</v>
       </c>
+      <c r="AF1">
+        <v>2051</v>
+      </c>
+      <c r="AG1">
+        <v>2052</v>
+      </c>
+      <c r="AH1">
+        <v>2053</v>
+      </c>
+      <c r="AI1">
+        <v>2054</v>
+      </c>
+      <c r="AJ1">
+        <v>2055</v>
+      </c>
+      <c r="AK1">
+        <v>2056</v>
+      </c>
+      <c r="AL1">
+        <v>2057</v>
+      </c>
+      <c r="AM1">
+        <v>2058</v>
+      </c>
+      <c r="AN1">
+        <v>2059</v>
+      </c>
+      <c r="AO1">
+        <v>2060</v>
+      </c>
+      <c r="AP1">
+        <v>2061</v>
+      </c>
+      <c r="AQ1">
+        <v>2062</v>
+      </c>
+      <c r="AR1">
+        <v>2063</v>
+      </c>
+      <c r="AS1">
+        <v>2064</v>
+      </c>
+      <c r="AT1">
+        <v>2065</v>
+      </c>
+      <c r="AU1">
+        <v>2066</v>
+      </c>
+      <c r="AV1">
+        <v>2067</v>
+      </c>
+      <c r="AW1">
+        <v>2068</v>
+      </c>
+      <c r="AX1">
+        <v>2069</v>
+      </c>
+      <c r="AY1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="H2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="K2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="L2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="M2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="N2" s="6">
-        <v>0.26</v>
-      </c>
-      <c r="O2" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="P2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>0</v>
-      </c>
-      <c r="R2" s="6">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6">
-        <v>0</v>
-      </c>
-      <c r="T2" s="6">
-        <v>0</v>
-      </c>
-      <c r="U2" s="6">
-        <v>0</v>
-      </c>
-      <c r="V2" s="6">
-        <v>0</v>
-      </c>
-      <c r="W2" s="6">
-        <v>0</v>
-      </c>
-      <c r="X2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="6">
-        <v>0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5">
+        <v>0</v>
+      </c>
+      <c r="X2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="5"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="H3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="K3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="L3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="M3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="N3" s="6">
-        <v>0.26</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="P3" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>0</v>
-      </c>
-      <c r="R3" s="6">
-        <v>0</v>
-      </c>
-      <c r="S3" s="6">
-        <v>0</v>
-      </c>
-      <c r="T3" s="6">
-        <v>0</v>
-      </c>
-      <c r="U3" s="6">
-        <v>0</v>
-      </c>
-      <c r="V3" s="6">
-        <v>0</v>
-      </c>
-      <c r="W3" s="6">
-        <v>0</v>
-      </c>
-      <c r="X3" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="6">
-        <v>0</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>0</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5">
+        <v>0</v>
+      </c>
+      <c r="W3" s="5">
+        <v>0</v>
+      </c>
+      <c r="X3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="5"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6">
-        <v>0</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-      <c r="N4" s="6">
-        <v>0</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6">
-        <v>0</v>
-      </c>
-      <c r="V4" s="6">
-        <v>0</v>
-      </c>
-      <c r="W4" s="6">
-        <v>0</v>
-      </c>
-      <c r="X4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="6">
-        <v>0</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5">
+        <v>0</v>
+      </c>
+      <c r="X4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="5"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52">
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:52">
       <c r="B7" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C255835-D2CA-4403-8823-9819BA3F6B81}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3314045-B15D-4491-8336-AA71AEA28892}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27410CAB-AF69-4BF0-9B1A-348171EF6757}"/>
 </file>
--- a/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
+++ b/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27720"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Richa.richa\Downloads\BPSfDSPC\BPSfDSPC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\India EPS\InputData\bldgs\BPSfDSPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{C4CD6C72-4998-4F43-948F-FC077E0F061A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E19FBF4E-07E7-4597-84B9-E1CCC548F6AD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82666B1-E486-4231-844E-CFB01D9499C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="7" r:id="rId1"/>
-    <sheet name="BPSfDSPV" sheetId="8" r:id="rId2"/>
+    <sheet name="BPSfDSPC" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -82,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,24 +434,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="61.5703125" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -459,10 +460,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -475,17 +476,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AZ7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>5</v>
       </c>
@@ -640,7 +641,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:52">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -796,7 +797,7 @@
       </c>
       <c r="AZ2" s="5"/>
     </row>
-    <row r="3" spans="1:52">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -952,7 +953,7 @@
       </c>
       <c r="AZ3" s="5"/>
     </row>
-    <row r="4" spans="1:52">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1108,13 +1109,13 @@
       </c>
       <c r="AZ4" s="5"/>
     </row>
-    <row r="5" spans="1:52">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:52">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:52">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
     </row>
   </sheetData>
@@ -1124,6 +1125,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
     <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
@@ -1267,12 +1274,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1283,13 +1284,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C255835-D2CA-4403-8823-9819BA3F6B81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3314045-B15D-4491-8336-AA71AEA28892}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3314045-B15D-4491-8336-AA71AEA28892}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C255835-D2CA-4403-8823-9819BA3F6B81}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27410CAB-AF69-4BF0-9B1A-348171EF6757}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27410CAB-AF69-4BF0-9B1A-348171EF6757}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>